--- a/sheetmetal-pipeline/input/parts_sample.xlsx
+++ b/sheetmetal-pipeline/input/parts_sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,37 +424,37 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>PlateLength</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>PlateWidth</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Thickness</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>FlangeLength</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>BendAngle</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>BendRadius</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>KFactor</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -479,26 +479,28 @@
           <t>BR-001</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mild_steel</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>100</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>60</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>30</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>90</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>2</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.38</v>
       </c>
       <c r="I2" t="n">
         <v>6</v>
@@ -516,26 +518,28 @@
           <t>BR-002</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>aluminum_5052</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>80</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>50</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>15</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>90</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>1.2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.38</v>
       </c>
       <c r="I3" t="n">
         <v>5</v>
@@ -553,26 +557,28 @@
           <t>BR-003</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>stainless_304</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>150</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>80</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>40</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>90</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.4</v>
       </c>
       <c r="I4" t="n">
         <v>8</v>
@@ -590,26 +596,28 @@
           <t>BR-004</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mild_steel</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>120</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>70</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>35</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>90</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.38</v>
       </c>
       <c r="I5" t="n">
         <v>6</v>
@@ -627,28 +635,30 @@
           <t>BR-005</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mild_steel</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>100</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>60</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>30</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>90</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.38</v>
       </c>
       <c r="I6" t="n">
         <v>6</v>
@@ -657,6 +667,45 @@
         <v>30</v>
       </c>
       <c r="K6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BR-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>unobtainium</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>60</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>30</v>
+      </c>
+      <c r="G7" t="n">
+        <v>90</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K7" t="n">
         <v>15</v>
       </c>
     </row>
